--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -808,688 +808,685 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9913,0.0011,0.0028,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0000,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.5127,0.0011,0.0007,0.6006</t>
-  </si>
-  <si>
-    <t>0.4546,0.0034,0.0008,0.5199</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9877,0.0015,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.9368,0.0008,0.0004,0.0389</t>
+  </si>
+  <si>
+    <t>0.0215,0.0012,0.0005,0.9918</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
+    <t>0.9998,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9828,0.0003,0.0099,0.0000</t>
+  </si>
+  <si>
+    <t>0.0449,0.0018,0.9485,0.0003</t>
+  </si>
+  <si>
+    <t>0.9408,0.0007,0.0772,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.0029,0.9927,0.0005</t>
+  </si>
+  <si>
+    <t>0.8916,0.0033,0.0815,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9976,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.9961,0.0039,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9596,0.0005,0.0351,0.0001</t>
+  </si>
+  <si>
+    <t>0.8193,0.0135,0.0651,0.0020</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0789,0.0011,0.9026,0.0004</t>
+  </si>
+  <si>
+    <t>0.2247,0.0000,0.8747,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.5414,0.5770,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.1204,0.8179,0.0199,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9992,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9890,0.0002,0.0133,0.0002</t>
+  </si>
+  <si>
+    <t>0.0829,0.9233,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9980,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9953,0.0063,0.0003</t>
+  </si>
+  <si>
+    <t>0.0054,0.0009,0.9827,0.0032</t>
+  </si>
+  <si>
+    <t>0.0089,0.0593,0.9600,0.0010</t>
+  </si>
+  <si>
+    <t>0.0069,0.0002,0.9872,0.0014</t>
+  </si>
+  <si>
+    <t>0.0016,0.0835,0.9913,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.0909,0.0071,0.0001,0.8897</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0229,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.0451,0.9789,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9942,0.0027</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.0533,0.9823,0.0025</t>
+  </si>
+  <si>
+    <t>0.9972,0.0021,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.0037,0.9970,0.0048</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9942,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0057,0.9897,0.0017</t>
+  </si>
+  <si>
+    <t>0.0029,0.0005,0.9917,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9453,0.0266,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.0814,0.0026,0.9300,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9789,0.3822,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9000,0.9804,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0278,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0021,0.9985</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0005,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.6073,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9965,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.6785,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.8308,0.6482,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9923,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.6317,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0017,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0044,0.0021,0.9947,0.0002</t>
+  </si>
+  <si>
+    <t>0.9753,0.0005,0.0050,0.0018</t>
+  </si>
+  <si>
+    <t>0.0202,0.0004,0.9865,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.9879,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4581,0.6471,0.0021,0.0000</t>
+  </si>
+  <si>
+    <t>0.0621,0.0321,0.7108,0.0053</t>
+  </si>
+  <si>
+    <t>0.9608,0.0002,0.0527,0.0000</t>
+  </si>
+  <si>
+    <t>0.1181,0.2421,0.1043,0.0485</t>
+  </si>
+  <si>
+    <t>0.1813,0.0521,0.2834,0.0042</t>
+  </si>
+  <si>
+    <t>0.0002,0.0547,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9684,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.6639,0.2670,0.0130,0.0001</t>
+  </si>
+  <si>
+    <t>0.7745,0.2646,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.8987,0.9926,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9455,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.0089,0.9885,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.0025,0.9933,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7721,0.0014,0.2219,0.0003</t>
+  </si>
+  <si>
+    <t>0.1263,0.0002,0.8688,0.0013</t>
+  </si>
+  <si>
+    <t>0.7024,0.0036,0.2043,0.0014</t>
+  </si>
+  <si>
+    <t>0.0807,0.0000,0.0001,0.9808</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.6309,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9989,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0464,0.9495,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8050,0.0001,0.0207,0.0768</t>
+  </si>
+  <si>
+    <t>0.0010,0.0013,0.9968,0.0083</t>
+  </si>
+  <si>
+    <t>0.9961,0.0000,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0286,0.6651,0.2975,0.0007</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.2880,0.1854,0.1493,0.0001</t>
+  </si>
+  <si>
+    <t>0.9781,0.0247,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0027,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5114,0.0013,0.4865,0.0003</t>
-  </si>
-  <si>
-    <t>0.1705,0.0028,0.8247,0.0001</t>
-  </si>
-  <si>
-    <t>0.1113,0.0005,0.9289,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0006,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.9893,0.0001,0.0141,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0274,0.9840,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8138,0.0005,0.2000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9384,0.0018,0.0329,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0817,0.0009,0.9263,0.0003</t>
-  </si>
-  <si>
-    <t>0.5751,0.0000,0.5691,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0001,0.0049,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0003,0.9949,0.0007</t>
-  </si>
-  <si>
-    <t>0.7879,0.3630,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2267,0.8192,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0023,0.9992,0.0021</t>
-  </si>
-  <si>
-    <t>0.0060,0.9922,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.9902,0.0009,0.0075,0.0001</t>
-  </si>
-  <si>
-    <t>0.4249,0.0003,0.6750,0.0005</t>
-  </si>
-  <si>
-    <t>0.2780,0.7553,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9984,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9961,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.0169,0.0001,0.9745,0.0006</t>
-  </si>
-  <si>
-    <t>0.0044,0.0043,0.9912,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0006,0.9929,0.0039</t>
-  </si>
-  <si>
-    <t>0.0003,0.9324,0.9697,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0029,0.9992,0.0007</t>
-  </si>
-  <si>
-    <t>0.0102,0.7263,0.0007,0.6914</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0508,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0119,0.9952,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0022,0.9965,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9994,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.1942,0.8969,0.0015</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9992,0.0088</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0003,0.0001</t>
+    <t>0.9993,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0013,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9805,0.0204,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9712,0.0295,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9920,0.0082,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0235,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0089,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9926,0.0079,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9977,0.0013,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0328,0.9972,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9977,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.0324,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0009,0.9981,0.0017</t>
+  </si>
+  <si>
+    <t>0.0004,0.0010,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.9631,0.0003,0.0318,0.0001</t>
+  </si>
+  <si>
+    <t>0.0161,0.0035,0.9716,0.0003</t>
+  </si>
+  <si>
+    <t>0.9033,0.0155,0.0411,0.0002</t>
+  </si>
+  <si>
+    <t>0.0071,0.0110,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.0810,0.0043,0.8871,0.0001</t>
+  </si>
+  <si>
+    <t>0.9936,0.0001,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0505,0.0222,0.8428,0.0016</t>
+  </si>
+  <si>
+    <t>0.0914,0.9356,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.9946,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0029,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0903,0.9285,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.2077,0.8629,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.4258,0.4378,0.0093,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9913,0.0008,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9204,0.0085,0.0337,0.0010</t>
+  </si>
+  <si>
+    <t>0.0851,0.0344,0.7177,0.0033</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9974,0.0084</t>
+  </si>
+  <si>
+    <t>0.0009,0.0101,0.9931,0.0024</t>
+  </si>
+  <si>
+    <t>0.0233,0.0053,0.9639,0.0004</t>
+  </si>
+  <si>
+    <t>0.4554,0.0005,0.6273,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.1548,0.9706,0.0016</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0016,0.0004,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9710,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0277,0.9981,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.0030,0.9947,0.0049</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.9951,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9991,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8989,0.0002,0.1998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9655,0.0095,0.0081,0.0001</t>
-  </si>
-  <si>
-    <t>0.0554,0.0015,0.9536,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9692,0.9801,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6766,0.9930,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0424,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0017,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0042,0.0001,0.0001,0.9984</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0005,0.9994</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9969,0.0297,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9937,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.8975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.5838,0.9896,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9577,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9935,0.1835,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0020,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0015,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0015</t>
-  </si>
-  <si>
-    <t>0.0030,0.0020,0.9945,0.0002</t>
-  </si>
-  <si>
-    <t>0.9492,0.0001,0.0316,0.0009</t>
-  </si>
-  <si>
-    <t>0.0060,0.0004,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0117,0.9882,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9975,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9175,0.1137,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.2290,0.0068,0.6427,0.0007</t>
-  </si>
-  <si>
-    <t>0.7818,0.0003,0.2391,0.0002</t>
-  </si>
-  <si>
-    <t>0.3060,0.3459,0.0308,0.0049</t>
-  </si>
-  <si>
-    <t>0.8860,0.0744,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.0013,0.0156,0.0036,0.9921</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9990,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8532,0.0802,0.0158,0.0000</t>
-  </si>
-  <si>
-    <t>0.8365,0.2110,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0013,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8850,0.9874,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.2227,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.0046,0.9769,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0036,0.9947,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8659,0.0011,0.1233,0.0003</t>
-  </si>
-  <si>
-    <t>0.0074,0.0000,0.9924,0.0007</t>
-  </si>
-  <si>
-    <t>0.3669,0.0018,0.5074,0.0029</t>
-  </si>
-  <si>
-    <t>0.0300,0.0001,0.0002,0.9903</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0028,0.0000,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.9986,0.7315,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9966,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.0938,0.8781,0.0096,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9813,0.0000,0.0019,0.0074</t>
-  </si>
-  <si>
-    <t>0.0008,0.0061,0.9951,0.0133</t>
-  </si>
-  <si>
-    <t>0.9851,0.0000,0.0016,0.0035</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0229,0.9668,0.0092,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9929,0.0031,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.5544,0.0293,0.1931,0.0001</t>
-  </si>
-  <si>
-    <t>0.9646,0.0218,0.0037,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0027,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0002,0.0006</t>
+    <t>0.9961,0.0026,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0015,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9973,0.0009,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9595,0.0203,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.6189,0.3736,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0019,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0028,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9963,0.0003,0.0002,0.0030</t>
-  </si>
-  <si>
-    <t>0.9989,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9075,0.1313,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9768,0.0037,0.0160,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0614,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.2891,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.0011,0.9938,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.0003,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.9522,0.0058,0.0133,0.0004</t>
-  </si>
-  <si>
-    <t>0.9257,0.0145,0.0246,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0190,0.9848,0.0000</t>
-  </si>
-  <si>
-    <t>0.8676,0.0008,0.1820,0.0000</t>
-  </si>
-  <si>
-    <t>0.9414,0.0009,0.0283,0.0009</t>
-  </si>
-  <si>
-    <t>0.0268,0.0012,0.9667,0.0008</t>
-  </si>
-  <si>
-    <t>0.2969,0.8062,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0486,0.9724,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0043,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1537,0.9057,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0191,0.9817,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.8767,0.0504,0.0081,0.0016</t>
-  </si>
-  <si>
-    <t>0.9954,0.0001,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.9876,0.0014,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.1341,0.1081,0.2835,0.0143</t>
-  </si>
-  <si>
-    <t>0.0733,0.0108,0.8332,0.0070</t>
-  </si>
-  <si>
-    <t>0.0011,0.0011,0.9963,0.0029</t>
-  </si>
-  <si>
-    <t>0.0037,0.0130,0.9802,0.0029</t>
-  </si>
-  <si>
-    <t>0.0046,0.2565,0.9647,0.0005</t>
-  </si>
-  <si>
-    <t>0.0701,0.0029,0.9245,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.0283,0.9468,0.0026</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0017,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0374,0.0663,0.8399,0.0011</t>
-  </si>
-  <si>
-    <t>0.9925,0.0008,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.0251,0.0000,0.9831,0.0000</t>
-  </si>
-  <si>
-    <t>0.0949,0.0018,0.9153,0.0001</t>
-  </si>
-  <si>
-    <t>0.0062,0.6909,0.7230,0.0056</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0318,0.0027,0.9516,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0005,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.1717,0.0116,0.7240,0.0006</t>
-  </si>
-  <si>
-    <t>0.8246,0.0009,0.1186,0.0009</t>
-  </si>
-  <si>
-    <t>0.9741,0.0000,0.0091,0.0004</t>
-  </si>
-  <si>
-    <t>0.9844,0.0009,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0028,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0022,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0156,0.9936,0.0004</t>
-  </si>
-  <si>
-    <t>0.0033,0.0019,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.8955,0.0001,0.1603,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0013,0.9961,0.0173</t>
-  </si>
-  <si>
-    <t>0.0010,0.0017,0.9958,0.0008</t>
-  </si>
-  <si>
-    <t>0.0268,0.0025,0.9565,0.0025</t>
-  </si>
-  <si>
-    <t>0.9573,0.0001,0.0024,0.0164</t>
-  </si>
-  <si>
-    <t>0.0001,0.0099,0.0001,0.9996</t>
-  </si>
-  <si>
-    <t>0.0145,0.0001,0.0002,0.9950</t>
+    <t>0.0000,0.0002,1.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0479,0.0305,0.8879,0.0023</t>
+  </si>
+  <si>
+    <t>0.8777,0.0004,0.0656,0.0050</t>
+  </si>
+  <si>
+    <t>0.0071,0.0001,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.1065,0.0016,0.8991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.1442,0.9747,0.0027</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0591,0.0007,0.9389,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.3353,0.0182,0.5047,0.0003</t>
+  </si>
+  <si>
+    <t>0.8165,0.0006,0.1266,0.0013</t>
+  </si>
+  <si>
+    <t>0.9386,0.0003,0.0379,0.0005</t>
+  </si>
+  <si>
+    <t>0.9941,0.0002,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0066,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0027,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0058,0.9937,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0008,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0025,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0801,0.0369,0.7288,0.0003</t>
+  </si>
+  <si>
+    <t>0.1225,0.0002,0.8922,0.0004</t>
+  </si>
+  <si>
+    <t>0.0063,0.0034,0.9461,0.0512</t>
+  </si>
+  <si>
+    <t>0.0095,0.0009,0.9860,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.0003,0.9931,0.0022</t>
+  </si>
+  <si>
+    <t>0.8933,0.0000,0.0066,0.0264</t>
+  </si>
+  <si>
+    <t>0.0001,0.0056,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0296,0.0000,0.0002,0.9919</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9976,0.0001,0.0002,0.0003</t>
+    <t>0.9882,0.0001,0.0001,0.0047</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,10 +1897,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1917,7 +1914,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1973,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1987,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2001,7 +1998,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2012,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2040,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2068,10 +2065,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2138,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2183,7 +2180,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2194,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2250,7 @@
         <v>259</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2278,10 +2275,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2292,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2320,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2348,10 +2345,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,7 +2390,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2432,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2446,10 +2443,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2488,10 +2485,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2824,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,7 +2838,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,10 +2863,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2894,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2908,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2964,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +2978,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +2992,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,10 +3003,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3020,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3034,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3048,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3062,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,10 +3073,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>273</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3174,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3188,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3328,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,10 +3451,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3471,7 +3468,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3482,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3493,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3507,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3524,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3580,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,7 +3622,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>271</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>273</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3748,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,10 +3759,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3776,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3790,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,7 +3818,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3832,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,10 +3843,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3874,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>392</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,7 +3916,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3947,7 +3944,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>271</v>
+        <v>394</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3975,7 +3972,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4003,7 +4000,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4070,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,10 +4109,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4199,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>271</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4280,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,7 +4308,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>420</v>
+        <v>321</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,10 +4515,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,10 +4529,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4549,7 +4546,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4563,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4574,10 +4571,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4588,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4616,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4644,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4658,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4686,10 +4683,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4714,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4728,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4745,7 +4742,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4784,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>321</v>
+        <v>453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>269</v>
+        <v>409</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,7 +4952,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,10 +5005,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5092,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5109,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>319</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>271</v>
+        <v>474</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5207,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>357</v>
+        <v>273</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5235,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,10 +5299,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5316,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>490</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5414,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>489</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,7 +5428,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
